--- a/src/main/resources/TestCases/HiringManagementSystem.xlsx
+++ b/src/main/resources/TestCases/HiringManagementSystem.xlsx
@@ -802,9 +802,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="true" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment wrapText="false" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment wrapText="true" vertical="top"/>
     </xf>
@@ -820,13 +826,13 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="5.0" customWidth="true"/>
-    <col min="2" max="2" width="20.0" customWidth="true"/>
-    <col min="3" max="3" width="30.0" customWidth="true"/>
-    <col min="4" max="4" width="30.0" customWidth="true"/>
-    <col min="5" max="5" width="40.0" customWidth="true"/>
-    <col min="6" max="6" width="58.59375" customWidth="true"/>
-    <col min="7" max="7" width="70.3125" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="5.0"/>
+    <col min="2" max="2" customWidth="true" width="20.0"/>
+    <col min="3" max="3" customWidth="true" width="30.0"/>
+    <col min="4" max="4" customWidth="true" width="30.0"/>
+    <col min="5" max="5" customWidth="true" width="40.0"/>
+    <col min="6" max="6" customWidth="true" width="58.59375"/>
+    <col min="7" max="7" customWidth="true" width="70.3125"/>
   </cols>
   <sheetData>
     <row r="1">
